--- a/data/trans_dic/P40_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P40_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,09</t>
+          <t>2,41; 5,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,01</t>
+          <t>1,14; 4,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,42</t>
+          <t>2,82; 7,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,62</t>
+          <t>0,74; 6,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 10,56</t>
+          <t>5,42; 10,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 10,87</t>
+          <t>5,26; 10,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,24</t>
+          <t>2,77; 6,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 17,13</t>
+          <t>7,87; 17,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,34</t>
+          <t>4,34; 7,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,5</t>
+          <t>3,52; 6,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,49</t>
+          <t>3,12; 6,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 9,59</t>
+          <t>4,84; 10,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,88</t>
+          <t>3,66; 6,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,66</t>
+          <t>4,73; 8,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,44</t>
+          <t>2,99; 6,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,79</t>
+          <t>4,28; 10,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,03</t>
+          <t>10,55; 15,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,49</t>
+          <t>6,78; 11,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,66</t>
+          <t>4,56; 8,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 52,82</t>
+          <t>4,64; 9,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,38</t>
+          <t>7,15; 10,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,49</t>
+          <t>6,26; 9,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,94</t>
+          <t>4,24; 6,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 35,08</t>
+          <t>5,17; 8,94</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 13,75</t>
+          <t>8,76; 13,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 12,29</t>
+          <t>7,49; 12,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,26</t>
+          <t>5,94; 10,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,53</t>
+          <t>5,74; 10,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,94</t>
+          <t>16,03; 22,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,62; 19,16</t>
+          <t>13,54; 19,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 13,01</t>
+          <t>8,1; 12,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 15,52</t>
+          <t>11,11; 15,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,29; 17,21</t>
+          <t>13,33; 17,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,42; 14,98</t>
+          <t>11,18; 15,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,88</t>
+          <t>7,65; 10,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 12,73</t>
+          <t>8,87; 12,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 16,64</t>
+          <t>10,49; 16,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,14; 18,45</t>
+          <t>12,08; 18,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,05; 18,78</t>
+          <t>13,08; 19,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 19,92</t>
+          <t>15,17; 21,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,38; 30,79</t>
+          <t>23,49; 30,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,36; 27,59</t>
+          <t>20,44; 27,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 24,52</t>
+          <t>17,9; 24,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,59; 26,09</t>
+          <t>20,91; 25,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 22,79</t>
+          <t>17,78; 22,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,22; 22,22</t>
+          <t>17,42; 22,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 20,71</t>
+          <t>16,47; 20,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,43; 21,97</t>
+          <t>18,74; 22,67</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,96; 33,78</t>
+          <t>24,52; 33,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,39; 32,09</t>
+          <t>22,83; 31,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,92; 27,83</t>
+          <t>19,94; 27,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,78; 34,0</t>
+          <t>25,94; 33,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,49; 44,08</t>
+          <t>34,13; 43,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,65; 42,99</t>
+          <t>33,26; 42,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,67; 42,87</t>
+          <t>33,21; 42,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,94; 38,33</t>
+          <t>32,29; 38,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,0; 37,54</t>
+          <t>30,56; 37,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,58; 36,32</t>
+          <t>29,48; 35,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,98; 34,23</t>
+          <t>27,87; 34,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,22; 35,05</t>
+          <t>30,07; 34,48</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,52; 41,16</t>
+          <t>29,66; 40,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,56; 40,03</t>
+          <t>28,21; 40,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,3; 36,37</t>
+          <t>26,13; 36,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,22; 33,51</t>
+          <t>25,3; 32,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,93; 64,15</t>
+          <t>53,69; 64,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,51; 55,19</t>
+          <t>43,83; 54,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,12; 54,75</t>
+          <t>44,19; 54,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,37; 43,78</t>
+          <t>39,59; 46,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,69; 52,37</t>
+          <t>44,61; 52,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38,58; 46,33</t>
+          <t>38,26; 45,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36,8; 44,53</t>
+          <t>37,08; 44,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,38; 37,45</t>
+          <t>33,58; 38,87</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,31%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,92; 61,35</t>
+          <t>46,68; 60,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48,36; 62,05</t>
+          <t>48,37; 61,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42,28; 53,72</t>
+          <t>42,28; 53,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41,3; 50,72</t>
+          <t>41,22; 51,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,21; 69,89</t>
+          <t>58,95; 70,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,7; 71,96</t>
+          <t>61,26; 71,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,54; 69,65</t>
+          <t>58,78; 69,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,01; 66,43</t>
+          <t>59,51; 66,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>56,18; 64,72</t>
+          <t>56,48; 64,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58,31; 66,26</t>
+          <t>58,43; 66,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53,89; 61,91</t>
+          <t>53,66; 62,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,97; 59,34</t>
+          <t>53,53; 58,87</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,71; 17,33</t>
+          <t>14,75; 17,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,39</t>
+          <t>15,55; 18,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,75; 17,31</t>
+          <t>14,71; 17,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,06; 19,84</t>
+          <t>17,4; 20,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,93; 30,15</t>
+          <t>27,01; 30,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,36; 28,47</t>
+          <t>25,47; 28,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,67; 26,78</t>
+          <t>23,74; 26,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,89; 31,29</t>
+          <t>26,29; 28,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,4; 23,37</t>
+          <t>21,3; 23,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21,05; 23,04</t>
+          <t>20,89; 23,09</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,77; 21,59</t>
+          <t>19,68; 21,74</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,98; 25,17</t>
+          <t>22,35; 24,11</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33899</t>
+          <t>44032</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44479</t>
+          <t>55264</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11997; 30109</t>
+          <t>11883; 29363</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5014; 17703</t>
+          <t>5022; 17943</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12575; 30930</t>
+          <t>11738; 30470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2614; 30493</t>
+          <t>3027; 25854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26979; 49362</t>
+          <t>25327; 46816</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23280; 45786</t>
+          <t>22140; 43239</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11018; 28494</t>
+          <t>10906; 26868</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20757; 53654</t>
+          <t>28521; 64573</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42416; 70594</t>
+          <t>41727; 70482</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30893; 56038</t>
+          <t>30356; 56814</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27016; 52583</t>
+          <t>25238; 50959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27103; 68430</t>
+          <t>37273; 79413</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>32766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>100229</t>
+          <t>34554</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>130829</t>
+          <t>67321</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26387; 50572</t>
+          <t>26886; 49821</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30713; 58255</t>
+          <t>31839; 60249</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16839; 37684</t>
+          <t>17482; 38331</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19461; 45716</t>
+          <t>20394; 48750</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65620; 100271</t>
+          <t>66020; 99553</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40243; 69434</t>
+          <t>40990; 70076</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25251; 48070</t>
+          <t>25325; 49331</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32566; 270180</t>
+          <t>23246; 48236</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98172; 141225</t>
+          <t>97279; 142472</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80654; 121212</t>
+          <t>79918; 119556</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47672; 79123</t>
+          <t>48396; 78735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60291; 327995</t>
+          <t>50566; 87439</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46762</t>
+          <t>47349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71819</t>
+          <t>82125</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>118581</t>
+          <t>129474</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55542; 87789</t>
+          <t>55929; 87974</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49611; 82695</t>
+          <t>50367; 84986</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38728; 68535</t>
+          <t>39701; 68884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34547; 61836</t>
+          <t>35618; 64126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>110395; 151316</t>
+          <t>110542; 153625</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96016; 135109</t>
+          <t>95493; 136555</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53681; 85093</t>
+          <t>52976; 84053</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58739; 84183</t>
+          <t>69147; 97436</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>176516; 228618</t>
+          <t>177128; 227522</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157355; 206388</t>
+          <t>154091; 206917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100841; 143817</t>
+          <t>101092; 143959</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>100860; 137288</t>
+          <t>110210; 149201</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120826</t>
+          <t>125975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>164981</t>
+          <t>171658</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>285807</t>
+          <t>297633</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55931; 86092</t>
+          <t>54278; 86041</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74074; 112578</t>
+          <t>73681; 113136</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83925; 120756</t>
+          <t>84145; 123407</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51031; 176818</t>
+          <t>106295; 147405</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>120570; 158789</t>
+          <t>121122; 159632</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>125262; 169697</t>
+          <t>125743; 169371</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>115580; 158114</t>
+          <t>115386; 159007</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>139550; 185866</t>
+          <t>153983; 189618</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183898; 235441</t>
+          <t>183637; 234084</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>210947; 272236</t>
+          <t>213389; 272596</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>208790; 266754</t>
+          <t>212145; 269260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>182837; 351614</t>
+          <t>269255; 325760</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170637</t>
+          <t>179097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>191129</t>
+          <t>215004</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>361766</t>
+          <t>394101</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>96284; 130308</t>
+          <t>94600; 129634</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99979; 137152</t>
+          <t>97570; 136284</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94109; 131451</t>
+          <t>94189; 129806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150276; 190803</t>
+          <t>158057; 201525</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>138994; 177683</t>
+          <t>137558; 176433</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>150690; 192495</t>
+          <t>148927; 191830</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>166518; 212000</t>
+          <t>164202; 209585</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>174987; 210022</t>
+          <t>196625; 232787</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>244569; 296086</t>
+          <t>241037; 294252</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258892; 317869</t>
+          <t>257982; 314951</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>270559; 331018</t>
+          <t>269445; 329256</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>335212; 388738</t>
+          <t>366339; 420065</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109801</t>
+          <t>119138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>171819</t>
+          <t>187945</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>281619</t>
+          <t>307084</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>89293; 120420</t>
+          <t>86771; 118856</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88489; 124007</t>
+          <t>87403; 124195</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87227; 120618</t>
+          <t>86649; 120782</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96516; 123357</t>
+          <t>102987; 132796</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>184482; 219450</t>
+          <t>183657; 220227</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>157571; 195374</t>
+          <t>155161; 193622</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>164866; 204622</t>
+          <t>165152; 202790</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>81330; 266316</t>
+          <t>173857; 203838</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>283632; 332365</t>
+          <t>283123; 331472</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256082; 307534</t>
+          <t>253988; 304044</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>259553; 314090</t>
+          <t>261550; 312795</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>150144; 365664</t>
+          <t>284180; 328907</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130058</t>
+          <t>142970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>269766</t>
+          <t>293292</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>399824</t>
+          <t>436261</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>98476; 128764</t>
+          <t>97970; 126108</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>120330; 154397</t>
+          <t>120357; 154156</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>108344; 137653</t>
+          <t>108350; 137640</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116780; 143420</t>
+          <t>127873; 159087</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>197720; 233354</t>
+          <t>196845; 234335</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>239354; 279132</t>
+          <t>237644; 278512</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>233463; 277795</t>
+          <t>234421; 278053</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>255531; 282880</t>
+          <t>276466; 307668</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>305512; 351964</t>
+          <t>307137; 352638</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>371328; 421949</t>
+          <t>372058; 421533</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>353051; 405594</t>
+          <t>351504; 406570</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>382435; 420455</t>
+          <t>414765; 456121</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>619265</t>
+          <t>658528</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1003641</t>
+          <t>1028610</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1622905</t>
+          <t>1687138</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>481701; 567352</t>
+          <t>483004; 563588</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>528047; 622007</t>
+          <t>526094; 622642</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>497444; 583985</t>
+          <t>496042; 586909</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>486494; 686297</t>
+          <t>614602; 707202</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>909699; 1018360</t>
+          <t>912314; 1019541</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>896634; 1006458</t>
+          <t>900356; 1007094</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>831911; 941096</t>
+          <t>834271; 941753</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>838084; 1145921</t>
+          <t>981802; 1075953</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1423286; 1554451</t>
+          <t>1416684; 1557011</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1455899; 1594040</t>
+          <t>1445032; 1597084</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1361681; 1486878</t>
+          <t>1355349; 1497447</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1422663; 1792229</t>
+          <t>1624541; 1752315</t>
         </is>
       </c>
     </row>
